--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79539</v>
+        <v>79540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78857</v>
+        <v>78858</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79540</v>
+        <v>79544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78858</v>
+        <v>78862</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79544</v>
+        <v>79545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78862</v>
+        <v>78863</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79545</v>
+        <v>79549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>79540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78863</v>
+        <v>78867</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79540</v>
+        <v>79546</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78867</v>
+        <v>78873</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79546</v>
+        <v>79559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136145947</v>
       </c>
       <c r="B33" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78873</v>
+        <v>78886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 32395-2026 artfynd.xlsx
+++ b/artfynd/A 32395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145950</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145936</v>
       </c>
       <c r="B3" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145949</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145968</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145940</v>
       </c>
       <c r="B6" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145952</v>
       </c>
       <c r="B7" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145960</v>
       </c>
       <c r="B8" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136145969</v>
       </c>
       <c r="B9" t="n">
-        <v>79568</v>
+        <v>79569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136145944</v>
       </c>
       <c r="B10" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136145971</v>
       </c>
       <c r="B11" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136145957</v>
       </c>
       <c r="B12" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136145927</v>
       </c>
       <c r="B13" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136145939</v>
       </c>
       <c r="B14" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136145937</v>
       </c>
       <c r="B15" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136145946</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136145970</v>
       </c>
       <c r="B17" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136145931</v>
       </c>
       <c r="B18" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136145955</v>
       </c>
       <c r="B19" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136145967</v>
       </c>
       <c r="B20" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136145945</v>
       </c>
       <c r="B21" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136145966</v>
       </c>
       <c r="B22" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136145941</v>
       </c>
       <c r="B23" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136145928</v>
       </c>
       <c r="B24" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136145932</v>
       </c>
       <c r="B25" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136145938</v>
       </c>
       <c r="B26" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136145942</v>
       </c>
       <c r="B27" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136145948</v>
       </c>
       <c r="B28" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136145956</v>
       </c>
       <c r="B29" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136145962</v>
       </c>
       <c r="B30" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136145963</v>
       </c>
       <c r="B31" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136145930</v>
       </c>
       <c r="B32" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136145935</v>
       </c>
       <c r="B34" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>136145964</v>
       </c>
       <c r="B35" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136145965</v>
       </c>
       <c r="B36" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136145929</v>
       </c>
       <c r="B37" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136145933</v>
       </c>
       <c r="B38" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>136145951</v>
       </c>
       <c r="B39" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136145953</v>
       </c>
       <c r="B40" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>136145959</v>
       </c>
       <c r="B41" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136145954</v>
       </c>
       <c r="B42" t="n">
-        <v>78886</v>
+        <v>78887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
